--- a/BASE_ELEVATTA_SHAREPOINT.xlsx
+++ b/BASE_ELEVATTA_SHAREPOINT.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAINEL" sheetId="1" r:id="Rddf0c9984f71471a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APONTAMENTOS" sheetId="2" r:id="Re58d85c2612e47ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FVS_REGISTROS" sheetId="3" r:id="R2f6f5845a0ae4e01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FVS_ITENS" sheetId="4" r:id="R948f59d5b4c44bff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MEDICOES" sheetId="5" r:id="R3f4d8bc707924199"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FOTOS" sheetId="6" r:id="R40ca46b1f4094819"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PACOTES" sheetId="7" r:id="R20cadb70d5714ca7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FUNCIONARIOS" sheetId="8" r:id="Re9ad11ff6e9c44df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="9" r:id="R9d74c6c6d3764027"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OBRAS" sheetId="10" r:id="R737c43314ebe4c30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EQUIPES" sheetId="11" r:id="R138ec67a9fc548a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRENTES_SERVICO" sheetId="12" r:id="R8c258ffe9e2e489a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FERRAMENTAS" sheetId="13" r:id="R39b33f9930a6432d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TERMOS_FERRAMENTAS" sheetId="14" r:id="R81b02755592f44fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOVIMENTOS_FERRAMENTAS" sheetId="15" r:id="Rb138109d52e34910"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORTACOES" sheetId="16" r:id="R84c3ae61223e439a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_OCORRENCIAS" sheetId="17" r:id="R57b5d803c37946c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AUDITORIA" sheetId="18" r:id="R4981d86654b04df3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USUARIOS" sheetId="19" r:id="Rec960c21db594e5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAINEL" sheetId="1" r:id="R960bee3bcb294347"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APONTAMENTOS" sheetId="2" r:id="Rf34261e0b10949ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FVS_REGISTROS" sheetId="3" r:id="Re379e9e87d47427d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FVS_ITENS" sheetId="4" r:id="Re4f271dd28544afd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MEDICOES" sheetId="5" r:id="Rf9876bcd56a04286"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FOTOS" sheetId="6" r:id="R03f321550bfd4e2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PACOTES" sheetId="7" r:id="R091790a0099d446e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FUNCIONARIOS" sheetId="8" r:id="R290cd529b0a044c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="9" r:id="Rbb8543cac819453f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OBRAS" sheetId="10" r:id="R6010a63178e1414a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EQUIPES" sheetId="11" r:id="R27c251710a474944"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRENTES_SERVICO" sheetId="12" r:id="R778d168eea0d4876"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FERRAMENTAS" sheetId="13" r:id="R02f0680517884170"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TERMOS_FERRAMENTAS" sheetId="14" r:id="R2f30df8ee7b24b63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOVIMENTOS_FERRAMENTAS" sheetId="15" r:id="R173055a7ecc245fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORTACOES" sheetId="16" r:id="R93b3600cb6e6478f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_OCORRENCIAS" sheetId="17" r:id="Re7194d5c07c34e40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AUDITORIA" sheetId="18" r:id="R5a901de6d8fb4cd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USUARIOS" sheetId="19" r:id="R8c9b3b87c05a4e8a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -332,7 +332,7 @@
         <x:color rgb="FF0B7A49"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE8F5EE"/>
         </x:patternFill>
       </x:fill>
@@ -343,7 +343,7 @@
         <x:color rgb="FFB45A08"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF3E8"/>
         </x:patternFill>
       </x:fill>
@@ -354,7 +354,7 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDECEC"/>
         </x:patternFill>
       </x:fill>
@@ -684,7 +684,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbPacotes" displayName="tbPacotes" ref="A4:G57" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="tbPacotes" displayName="tbPacotes" ref="A4:G59" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="CODIGO"/>
     <x:tableColumn id="2" name="PACOTE_SERVICO"/>
@@ -1006,7 +1006,7 @@
       </x:c>
       <x:c r="B6" s="57" t="n">
         <x:f>COUNTA(PACOTES!A5:A500)</x:f>
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="56" t="str">
         <x:v>fonte única para Apontamento/FVS/Ferramentas</x:v>
@@ -1418,7 +1418,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5307da67dad54d6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3666eef5c9254782"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1490,7 +1490,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R566135459c7c41bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dd33e3002d44268"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1597,7 +1597,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R507fc3b5f705435c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f6d6dba169c47e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3184,7 +3184,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3895cb8d512c4f57"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c4605903b334780"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3354,7 +3354,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R621bafcb6f0f4c40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc4225053c874a3a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3545,7 +3545,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1f4d636976d445a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86e8d8760a974cc4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3680,7 +3680,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4261bf2de3814dd5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e569c899edb45dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3794,7 +3794,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c9d3667831a4483"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7483a2815e274138"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3894,7 +3894,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca6f656ca7b84e99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb6d68cd6471477f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3973,7 +3973,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27971115af1c4d16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25edc193570b411d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4171,7 +4171,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e9bdb36ff9d4f6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bab468f870e4167"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4361,7 +4361,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8272886c9ef541b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8b65470322141b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4474,7 +4474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R268ffe1f96af40ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8edec4b340749dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54587,7 +54587,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9bc4369fa974d0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra80007733c254fdb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54722,7 +54722,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R052f73bb09334b12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf64a87787a8346ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -55898,6 +55898,48 @@
         <x:v>2026-08-28T22:44:02</x:v>
       </x:c>
     </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str">
+        <x:v>GER-BETO</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>Betoneira</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>13 - Serviços gerais</x:v>
+      </x:c>
+      <x:c r="D58"/>
+      <x:c r="E58" t="str">
+        <x:v>Em andamento</x:v>
+      </x:c>
+      <x:c r="F58" t="str">
+        <x:v>SIM</x:v>
+      </x:c>
+      <x:c r="G58" t="str">
+        <x:v>2026-09-11T08:59:00</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str">
+        <x:v>GER-INDI</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>Serviços indiretos</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>13 - Serviços gerais</x:v>
+      </x:c>
+      <x:c r="D59"/>
+      <x:c r="E59" t="str">
+        <x:v>Em andamento</x:v>
+      </x:c>
+      <x:c r="F59" t="str">
+        <x:v>SIM</x:v>
+      </x:c>
+      <x:c r="G59" t="str">
+        <x:v>2026-09-11T08:59:00</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
@@ -55905,7 +55947,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a60bba84d2742bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcbb837388834663"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -56734,7 +56776,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R190d24ddc90045d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e2c2e10544c4ef2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -56826,7 +56868,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea2dff85a3e64fe8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3a3981b34f34011"/>
   </x:tableParts>
 </x:worksheet>
 </file>